--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.66292125004097</v>
+        <v>7.257724703131658</v>
       </c>
       <c r="D2" t="n">
-        <v>44.82173754995727</v>
+        <v>7.283532351868057</v>
       </c>
       <c r="E2" t="n">
-        <v>27.23859770563169</v>
+        <v>4.42627212716515</v>
       </c>
       <c r="F2" t="n">
-        <v>26.79098211029448</v>
+        <v>4.353534592922853</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>99.14011666130435</v>
+        <v>16.11026895746196</v>
       </c>
       <c r="D3" t="n">
-        <v>98.40370177054622</v>
+        <v>15.99060153771376</v>
       </c>
       <c r="E3" t="n">
-        <v>27.23859770563169</v>
+        <v>4.42627212716515</v>
       </c>
       <c r="F3" t="n">
-        <v>26.79098211029448</v>
+        <v>4.353534592922853</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
